--- a/TOTAL_RESULT.xlsx
+++ b/TOTAL_RESULT.xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOTAL_RESULTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DiffusionForensics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diffusion1kStep" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DiffusionForensics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diffusion1kStep" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline_vs_Improved" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +437,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Xem các sheet: TOTAL_RESULTS, DiffusionForensics, Diffusion1kStep.</t>
+          <t>Xem các sheet: TOTAL_RESULTS (số liệu), Baseline_vs_Improved (so sánh), DiffusionForensics (chi tiết), Diffusion1kStep (chi tiết), Notes (mô tả).</t>
         </is>
       </c>
     </row>
@@ -460,52 +468,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ROC_AUC</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Real_Acc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Fake_Acc</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Samples</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2351,1236 +2359,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>table</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>acc</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>auc_roc</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>auc_pr</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>fpr</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>generalization_gap_from_ref_acc</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ROC_AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Real_Acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Fake_Acc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
+          <t>Overall Mean</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>biggan</t>
+          <t>Trained (30 epochs)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>84.23</t>
+          <t>85.40%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>91.15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>53600</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Trung bình 3 datasets chính (ForenSynths + UniversalFakeDetect + GANGen-Detection)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>cyclegan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>85.92</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>98.91</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>98.57</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>nan</t>
+          <t>IMPROVEMENTS (Baseline → Trained):</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
+          <t>ForenSynths</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>deepfake</t>
+          <t>Improvement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>68.09</t>
+          <t>+53.30%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.56</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>46.7% → 100.0% (vượt mục tiêu 72-75%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
+          <t>Target Achievement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gaugan</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>EXCEEDED</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>87.40</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Vượt mục tiêu +25-28%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>progan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>99.61</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>99.96</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>99.97</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nan</t>
+          <t>TRAINING CONFIGURATION:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>stargan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>99.72</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nan</t>
+          <t>DATASET STATISTICS:</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>stylegan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>96.22</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>99.93</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>99.94</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>nan</t>
+          <t>PERFORMANCE ANALYSIS:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Table1_ForenSynths_Test</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>stylegan2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>97.18</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>99.94</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>99.95</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AttGAN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>91.05</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>95.68</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>97.17</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BEGAN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>50.12</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>75.48</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>83.55</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>49.88</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CramerGAN</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>52.18</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>89.20</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>90.77</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>47.83</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>InfoMaxGAN</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>52.18</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>78.79</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>79.79</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>47.83</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MMDGAN</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>52.18</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>86.91</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>88.38</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>47.83</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>RelGAN</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>99.85</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S3GAN</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>78.38</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>86.85</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>85.60</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SNGAN</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>52.18</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>85.07</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>86.53</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>47.83</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Table2_GANGen_Detection</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>STGAN</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>92.67</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>92.46</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>43.43</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Table3_DiffusionForensics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>adm</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>84.10</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>98.46</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>98.42</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Table3_DiffusionForensics</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>sdv1_new</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>94.51</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>99.66</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>99.81</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>dalle</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>85.85</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>97.58</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>97.41</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>glide_100_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>96.45</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>98.83</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>99.10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>glide_100_27</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>95.85</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>99.17</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>99.24</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>glide_50_27</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>96.75</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>99.12</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>99.28</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>guided</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>78.60</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>87.61</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>87.92</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>12.55</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ldm_100</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>97.00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>99.57</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>99.47</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ldm_200</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>97.40</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>99.57</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>99.48</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Table4_UniversalFakeDetect</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ldm_200_cfg</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>96.75</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>99.41</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Table5_Diffusion1kStep</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DALLE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>68.95</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>76.92</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>77.56</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Table5_Diffusion1kStep</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ddpm</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>75.11</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>83.67</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>78.44</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>9.60</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Table5_Diffusion1kStep</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>guided-diffusion</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>74.30</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>84.15</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>83.00</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Table5_Diffusion1kStep</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>improved-diffusion</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>76.10</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>85.08</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>87.14</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Table5_Diffusion1kStep</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>midjourney</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>78.97</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>87.64</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>88.06</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>nan</t>
+          <t>RECOMMENDATIONS:</t>
         </is>
       </c>
     </row>
@@ -3608,37 +2641,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>subset</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>auc_roc</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>auc_pr</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fpr</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>generalization_gap_from_ref_acc</t>
         </is>
@@ -4825,6 +3858,1402 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>subset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>auc_roc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>auc_pr</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fpr</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>generalization_gap_from_ref_acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>biggan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>84.23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>92.38</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>91.15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cyclegan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>85.92</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>98.91</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>98.57</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>deepfake</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>68.09</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>74.50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>70.56</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18.02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gaugan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>80.25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>87.40</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>84.27</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13.30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>progan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>99.61</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>99.96</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>99.97</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stargan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>99.72</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stylegan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>96.22</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>99.93</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>99.94</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Table1_ForenSynths_Test</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>stylegan2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>97.18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>99.94</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>99.95</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AttGAN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>91.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95.68</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>97.17</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BEGAN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>50.12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>75.48</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>83.55</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>49.88</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CramerGAN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>52.18</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>89.20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>90.77</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>47.83</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>InfoMaxGAN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>52.18</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>78.79</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>79.79</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>47.83</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MMDGAN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>52.18</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>86.91</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>88.38</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>47.83</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RelGAN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>99.85</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S3GAN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>78.38</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>86.85</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>85.60</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>12.75</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SNGAN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>52.18</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>85.07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>86.53</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>47.83</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Table2_GANGen_Detection</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STGAN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>56.57</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>92.67</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>92.46</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>43.43</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Table3_DiffusionForensics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>84.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>98.46</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>98.42</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Table3_DiffusionForensics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sdv1_new</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>94.51</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>99.66</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>99.81</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dalle</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>85.85</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>97.58</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>97.41</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>glide_100_10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>96.45</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>98.83</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>99.10</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>glide_100_27</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>99.17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>99.24</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>glide_50_27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>96.75</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>99.12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>99.28</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>guided</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>78.60</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>87.61</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>87.92</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ldm_100</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>99.57</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>99.47</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ldm_200</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>97.40</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>99.57</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>99.48</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Table4_UniversalFakeDetect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ldm_200_cfg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>96.75</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>99.42</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>99.41</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Table5_Diffusion1kStep</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DALLE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>68.95</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>76.92</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>77.56</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Table5_Diffusion1kStep</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ddpm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>75.11</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>83.67</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>78.44</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>9.60</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Table5_Diffusion1kStep</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>guided-diffusion</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>74.30</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>84.15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>83.00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Table5_Diffusion1kStep</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>improved-diffusion</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>76.10</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>85.08</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>87.14</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Table5_Diffusion1kStep</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>midjourney</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>78.97</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>87.64</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>88.06</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10.95</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Improved Acc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Δ Accuracy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline AP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Improved AP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Δ AP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline ROC-AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Improved ROC-AUC</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Δ ROC-AUC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ForenSynths Val</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>46.70%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+53.30%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sau khi train trên ForenSynths</t>
         </is>
       </c>
     </row>
